--- a/prix/basin.xlsx
+++ b/prix/basin.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\site-internet\peintures\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\pages-GitHub Braconnier\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9043461E-912C-4D59-AE4C-498CE31F8FB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{645CCA19-1F9D-437D-B20D-A557DE2DAD39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="73">
   <si>
     <t>path</t>
   </si>
@@ -255,9 +255,6 @@
   </si>
   <si>
     <t>basin/vitrificateur-2-composants-acryl.png</t>
-  </si>
-  <si>
-    <t>test</t>
   </si>
 </sst>
 </file>
@@ -317,7 +314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -351,6 +348,12 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1053,13 +1056,13 @@
       <c r="C19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="14">
         <v>23.46</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="13">
         <v>5</v>
       </c>
     </row>
@@ -1073,13 +1076,13 @@
       <c r="C20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="14">
         <v>18.39</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F20" s="13">
         <v>2</v>
       </c>
     </row>
@@ -1093,13 +1096,13 @@
       <c r="C21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="14">
         <v>32.450000000000003</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F21" s="11">
+      <c r="F21" s="13">
         <v>5</v>
       </c>
     </row>
@@ -1113,13 +1116,13 @@
       <c r="C22" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="14">
         <v>76.8</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="13">
         <v>6</v>
       </c>
     </row>
@@ -1133,13 +1136,13 @@
       <c r="C23" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="14">
         <v>72.45</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="F23" s="11">
+      <c r="F23" s="13">
         <v>5</v>
       </c>
     </row>
@@ -1153,13 +1156,13 @@
       <c r="C24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="14">
         <v>34.410000000000004</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F24" s="11">
+      <c r="F24" s="13">
         <v>10</v>
       </c>
     </row>
@@ -1173,13 +1176,13 @@
       <c r="C25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="14">
         <v>34.450000000000003</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F25" s="11">
+      <c r="F25" s="13">
         <v>5</v>
       </c>
     </row>
@@ -1193,13 +1196,13 @@
       <c r="C26" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="14">
         <v>76.900000000000006</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F26" s="11">
+      <c r="F26" s="13">
         <v>4</v>
       </c>
     </row>
@@ -1213,21 +1216,19 @@
       <c r="C27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="14">
         <v>48.18</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="F27" s="11">
+      <c r="F27" s="13">
         <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
-      <c r="B28" s="9" t="s">
-        <v>73</v>
-      </c>
+      <c r="B28" s="9"/>
       <c r="D28" s="10"/>
       <c r="E28" s="9"/>
       <c r="F28" s="11"/>

--- a/prix/basin.xlsx
+++ b/prix/basin.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\pages-GitHub Braconnier\peintures\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{645CCA19-1F9D-437D-B20D-A557DE2DAD39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19036F9A-A05E-4BD1-853E-92D3930ABE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -350,10 +350,10 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -733,13 +733,13 @@
       <c r="C2" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="13">
         <v>24.2</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="14">
         <v>13</v>
       </c>
     </row>
@@ -753,13 +753,13 @@
       <c r="C3" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="13">
         <v>24.2</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="14">
         <v>6</v>
       </c>
     </row>
@@ -773,13 +773,13 @@
       <c r="C4" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="13">
         <v>24.2</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="14">
         <v>3</v>
       </c>
     </row>
@@ -793,13 +793,13 @@
       <c r="C5" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="13">
         <v>26.2</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="14">
         <v>4</v>
       </c>
     </row>
@@ -813,13 +813,13 @@
       <c r="C6" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="13">
         <v>113.62</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="14">
         <v>1</v>
       </c>
     </row>
@@ -833,13 +833,13 @@
       <c r="C7" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="13">
         <v>61.2</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="14">
         <v>2</v>
       </c>
     </row>
@@ -851,13 +851,13 @@
       <c r="C8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="13">
         <v>103.24000000000001</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="14">
         <v>0</v>
       </c>
     </row>
@@ -869,13 +869,13 @@
       <c r="C9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="13">
         <v>32</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="14">
         <v>10</v>
       </c>
     </row>
@@ -884,13 +884,13 @@
       <c r="B10" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="13">
         <v>32</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="14">
         <v>0</v>
       </c>
     </row>
@@ -902,13 +902,13 @@
       <c r="C11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="13">
         <v>32</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="14">
         <v>3</v>
       </c>
     </row>
@@ -922,13 +922,13 @@
       <c r="C12" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="13">
         <v>95.83</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="14">
         <v>5</v>
       </c>
     </row>
@@ -942,14 +942,14 @@
       <c r="C13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="13">
         <v>183.18</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="11">
-        <v>12</v>
+      <c r="F13" s="14">
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -962,13 +962,13 @@
       <c r="C14" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="13">
         <v>86.29</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="14">
         <v>5</v>
       </c>
     </row>
@@ -982,14 +982,14 @@
       <c r="C15" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="13">
         <v>205.25</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F15" s="11">
-        <v>6</v>
+      <c r="F15" s="14">
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -1000,14 +1000,14 @@
       <c r="C16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="13">
         <v>7.41</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="F16" s="11">
-        <v>4</v>
+      <c r="F16" s="14">
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1018,14 +1018,14 @@
       <c r="C17" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="13">
         <v>16.7</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="11">
-        <v>0</v>
+      <c r="F17" s="14">
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1036,13 +1036,13 @@
       <c r="C18" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="13">
         <v>181.98</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="14">
         <v>1</v>
       </c>
     </row>
@@ -1056,13 +1056,13 @@
       <c r="C19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="13">
         <v>23.46</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="14">
         <v>5</v>
       </c>
     </row>
@@ -1076,13 +1076,13 @@
       <c r="C20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="13">
         <v>18.39</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="14">
         <v>2</v>
       </c>
     </row>
@@ -1096,13 +1096,13 @@
       <c r="C21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="13">
         <v>32.450000000000003</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="14">
         <v>5</v>
       </c>
     </row>
@@ -1116,13 +1116,13 @@
       <c r="C22" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="13">
         <v>76.8</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="14">
         <v>6</v>
       </c>
     </row>
@@ -1136,14 +1136,14 @@
       <c r="C23" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="13">
         <v>72.45</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="F23" s="13">
-        <v>5</v>
+      <c r="F23" s="14">
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -1156,13 +1156,13 @@
       <c r="C24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="13">
         <v>34.410000000000004</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="14">
         <v>10</v>
       </c>
     </row>
@@ -1176,13 +1176,13 @@
       <c r="C25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="13">
         <v>34.450000000000003</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25" s="14">
         <v>5</v>
       </c>
     </row>
@@ -1196,13 +1196,13 @@
       <c r="C26" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="13">
         <v>76.900000000000006</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="14">
         <v>4</v>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="C27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="13">
         <v>48.18</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="F27" s="13">
-        <v>3</v>
+      <c r="F27" s="14">
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/basin.xlsx
+++ b/prix/basin.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19036F9A-A05E-4BD1-853E-92D3930ABE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{202ACA4D-6849-4C93-9C96-D89AEF3C4197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -969,7 +969,7 @@
         <v>47</v>
       </c>
       <c r="F14" s="14">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -1103,7 +1103,7 @@
         <v>54</v>
       </c>
       <c r="F21" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -1223,7 +1223,7 @@
         <v>60</v>
       </c>
       <c r="F27" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/basin.xlsx
+++ b/prix/basin.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{202ACA4D-6849-4C93-9C96-D89AEF3C4197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB369544-6077-449C-8C9E-3834B0C24DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -929,7 +929,7 @@
         <v>45</v>
       </c>
       <c r="F12" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -963,13 +963,13 @@
         <v>6</v>
       </c>
       <c r="D14" s="13">
-        <v>86.29</v>
+        <v>83.2</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F14" s="14">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -1001,13 +1001,13 @@
         <v>64</v>
       </c>
       <c r="D16" s="13">
-        <v>7.41</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>49</v>
       </c>
       <c r="F16" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1019,13 +1019,13 @@
         <v>7</v>
       </c>
       <c r="D17" s="13">
-        <v>16.7</v>
+        <v>18</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1223,7 +1223,7 @@
         <v>60</v>
       </c>
       <c r="F27" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
